--- a/web_app/Album1_Dance_Production_Spec.xlsx
+++ b/web_app/Album1_Dance_Production_Spec.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -110,6 +110,12 @@
       <name val="Microsoft JhengHei"/>
       <b val="1"/>
       <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -203,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -285,6 +291,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6909,12 +6921,12 @@
       </c>
       <c r="H5" s="25" t="inlineStr">
         <is>
-          <t>images/track_03/a1_s03_seg01_girl.jpg</t>
+          <t>images/track_03/a1_s03_seg01_boy.jpg</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>a1_s03_seg01_girl.jpg ~ a1_s03_seg22_girl.jpg (共 22 張)</t>
+          <t>a1_s03_seg01_boy.jpg ~ a1_s03_seg22_boy.jpg (共 22 張)</t>
         </is>
       </c>
       <c r="J5" s="24" t="inlineStr">
@@ -22030,7 +22042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22044,6 +22056,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -22109,6 +22122,11 @@
           <t>首張圖片路徑 (9:16 720p)</t>
         </is>
       </c>
+      <c r="L2" s="28" t="inlineStr">
+        <is>
+          <t>AI 影片動畫路徑 (T3 目錄)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -22159,7 +22177,12 @@
       </c>
       <c r="K3" s="20" t="inlineStr">
         <is>
-          <t>images/track_03/a1_s03_seg01_girl.jpg</t>
+          <t>images/track_03/a1_s03_seg01_boy.jpg</t>
+        </is>
+      </c>
+      <c r="L3" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_01.mp4</t>
         </is>
       </c>
     </row>
@@ -22215,6 +22238,11 @@
           <t>images/track_03/a1_s03_seg02_girl.jpg</t>
         </is>
       </c>
+      <c r="L4" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_02.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
@@ -22268,6 +22296,11 @@
           <t>images/track_03/a1_s03_seg03_girl.jpg</t>
         </is>
       </c>
+      <c r="L5" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_03.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -22321,6 +22354,11 @@
           <t>images/track_03/a1_s03_seg04_girl.jpg</t>
         </is>
       </c>
+      <c r="L6" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_04.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -22374,6 +22412,11 @@
           <t>images/track_03/a1_s03_seg05_girl.jpg</t>
         </is>
       </c>
+      <c r="L7" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_05.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -22427,6 +22470,11 @@
           <t>images/track_03/a1_s03_seg06_girl.jpg</t>
         </is>
       </c>
+      <c r="L8" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_06.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -22480,6 +22528,11 @@
           <t>images/track_03/a1_s03_seg07_girl.jpg</t>
         </is>
       </c>
+      <c r="L9" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_07.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -22533,6 +22586,11 @@
           <t>images/track_03/a1_s03_seg08_girl.jpg</t>
         </is>
       </c>
+      <c r="L10" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_08.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -22586,6 +22644,11 @@
           <t>images/track_03/a1_s03_seg09_girl.jpg</t>
         </is>
       </c>
+      <c r="L11" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_09.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -22639,6 +22702,11 @@
           <t>images/track_03/a1_s03_seg10_girl.jpg</t>
         </is>
       </c>
+      <c r="L12" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_10.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -22692,6 +22760,11 @@
           <t>images/track_03/a1_s03_seg11_girl.jpg</t>
         </is>
       </c>
+      <c r="L13" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_11.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -22745,6 +22818,11 @@
           <t>images/track_03/a1_s03_seg12_girl.jpg</t>
         </is>
       </c>
+      <c r="L14" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_12.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -22798,6 +22876,11 @@
           <t>images/track_03/a1_s03_seg13_girl.jpg</t>
         </is>
       </c>
+      <c r="L15" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_13.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -22851,6 +22934,11 @@
           <t>images/track_03/a1_s03_seg14_girl.jpg</t>
         </is>
       </c>
+      <c r="L16" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_14.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -22904,6 +22992,11 @@
           <t>images/track_03/a1_s03_seg15_girl.jpg</t>
         </is>
       </c>
+      <c r="L17" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_15.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -22957,6 +23050,11 @@
           <t>images/track_03/a1_s03_seg16_girl.jpg</t>
         </is>
       </c>
+      <c r="L18" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_16.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -23010,6 +23108,11 @@
           <t>images/track_03/a1_s03_seg17_girl.jpg</t>
         </is>
       </c>
+      <c r="L19" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_17.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -23063,6 +23166,11 @@
           <t>images/track_03/a1_s03_seg18_girl.jpg</t>
         </is>
       </c>
+      <c r="L20" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_18.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -23116,6 +23224,11 @@
           <t>images/track_03/a1_s03_seg19_girl.jpg</t>
         </is>
       </c>
+      <c r="L21" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_19.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -23169,6 +23282,11 @@
           <t>images/track_03/a1_s03_seg20_girl.jpg</t>
         </is>
       </c>
+      <c r="L22" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_20.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -23222,6 +23340,11 @@
           <t>images/track_03/a1_s03_seg21_girl.jpg</t>
         </is>
       </c>
+      <c r="L23" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_21.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -23273,6 +23396,11 @@
       <c r="K24" s="20" t="inlineStr">
         <is>
           <t>images/track_03/a1_s03_seg22_girl.jpg</t>
+        </is>
+      </c>
+      <c r="L24" s="29" t="inlineStr">
+        <is>
+          <t>videos/T3/t3_seg_22.mp4</t>
         </is>
       </c>
     </row>

--- a/web_app/Album1_Dance_Production_Spec.xlsx
+++ b/web_app/Album1_Dance_Production_Spec.xlsx
@@ -6983,12 +6983,12 @@
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>images/track_04/a1_s04_seg01_boy.jpg</t>
+          <t>images/track_04/a1_s04_seg01_girl.jpg</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>a1_s04_seg01_boy.jpg ~ a1_s04_seg26_boy.jpg (共 26 張)</t>
+          <t>a1_s04_seg01_girl.jpg ~ a1_s04_seg26_girl.jpg (共 26 張)</t>
         </is>
       </c>
       <c r="J6" s="24" t="inlineStr">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="K3" s="20" t="inlineStr">
         <is>
-          <t>images/track_04/a1_s04_seg01_boy.jpg</t>
+          <t>images/track_04/a1_s04_seg01_girl.jpg</t>
         </is>
       </c>
     </row>

--- a/web_app/Album1_Dance_Production_Spec.xlsx
+++ b/web_app/Album1_Dance_Production_Spec.xlsx
@@ -23418,7 +23418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23432,6 +23432,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -23497,6 +23498,11 @@
           <t>首張圖片路徑 (9:16 720p)</t>
         </is>
       </c>
+      <c r="L2" s="28" t="inlineStr">
+        <is>
+          <t>AI 影片動畫路徑 (T4 目錄)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -23550,6 +23556,11 @@
           <t>images/track_04/a1_s04_seg01_girl.jpg</t>
         </is>
       </c>
+      <c r="L3" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_01.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -23603,6 +23614,11 @@
           <t>images/track_04/a1_s04_seg02_boy.jpg</t>
         </is>
       </c>
+      <c r="L4" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_02.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
@@ -23656,6 +23672,11 @@
           <t>images/track_04/a1_s04_seg03_boy.jpg</t>
         </is>
       </c>
+      <c r="L5" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_03.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -23709,6 +23730,11 @@
           <t>images/track_04/a1_s04_seg04_boy.jpg</t>
         </is>
       </c>
+      <c r="L6" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_04.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -23762,6 +23788,11 @@
           <t>images/track_04/a1_s04_seg05_boy.jpg</t>
         </is>
       </c>
+      <c r="L7" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_05.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -23815,6 +23846,11 @@
           <t>images/track_04/a1_s04_seg06_boy.jpg</t>
         </is>
       </c>
+      <c r="L8" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_06.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -23868,6 +23904,11 @@
           <t>images/track_04/a1_s04_seg07_boy.jpg</t>
         </is>
       </c>
+      <c r="L9" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_07.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -23921,6 +23962,11 @@
           <t>images/track_04/a1_s04_seg08_boy.jpg</t>
         </is>
       </c>
+      <c r="L10" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_08.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -23974,6 +24020,11 @@
           <t>images/track_04/a1_s04_seg09_boy.jpg</t>
         </is>
       </c>
+      <c r="L11" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_09.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -24027,6 +24078,11 @@
           <t>images/track_04/a1_s04_seg10_boy.jpg</t>
         </is>
       </c>
+      <c r="L12" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_10.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -24080,6 +24136,11 @@
           <t>images/track_04/a1_s04_seg11_boy.jpg</t>
         </is>
       </c>
+      <c r="L13" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_11.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -24133,6 +24194,11 @@
           <t>images/track_04/a1_s04_seg12_boy.jpg</t>
         </is>
       </c>
+      <c r="L14" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_12.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -24186,6 +24252,11 @@
           <t>images/track_04/a1_s04_seg13_boy.jpg</t>
         </is>
       </c>
+      <c r="L15" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_13.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -24239,6 +24310,11 @@
           <t>images/track_04/a1_s04_seg14_boy.jpg</t>
         </is>
       </c>
+      <c r="L16" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_14.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -24292,6 +24368,11 @@
           <t>images/track_04/a1_s04_seg15_boy.jpg</t>
         </is>
       </c>
+      <c r="L17" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_15.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -24345,6 +24426,11 @@
           <t>images/track_04/a1_s04_seg16_boy.jpg</t>
         </is>
       </c>
+      <c r="L18" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_16.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -24398,6 +24484,11 @@
           <t>images/track_04/a1_s04_seg17_boy.jpg</t>
         </is>
       </c>
+      <c r="L19" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_17.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -24451,6 +24542,11 @@
           <t>images/track_04/a1_s04_seg18_boy.jpg</t>
         </is>
       </c>
+      <c r="L20" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_18.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -24504,6 +24600,11 @@
           <t>images/track_04/a1_s04_seg19_boy.jpg</t>
         </is>
       </c>
+      <c r="L21" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_19.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -24557,6 +24658,11 @@
           <t>images/track_04/a1_s04_seg20_boy.jpg</t>
         </is>
       </c>
+      <c r="L22" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_20.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -24610,6 +24716,11 @@
           <t>images/track_04/a1_s04_seg21_boy.jpg</t>
         </is>
       </c>
+      <c r="L23" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_21.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -24663,6 +24774,11 @@
           <t>images/track_04/a1_s04_seg22_boy.jpg</t>
         </is>
       </c>
+      <c r="L24" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_22.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -24716,6 +24832,11 @@
           <t>images/track_04/a1_s04_seg23_boy.jpg</t>
         </is>
       </c>
+      <c r="L25" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_23.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
@@ -24769,6 +24890,11 @@
           <t>images/track_04/a1_s04_seg24_boy.jpg</t>
         </is>
       </c>
+      <c r="L26" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_24.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -24822,6 +24948,11 @@
           <t>images/track_04/a1_s04_seg25_boy.jpg</t>
         </is>
       </c>
+      <c r="L27" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_25.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -24873,6 +25004,11 @@
       <c r="K28" s="20" t="inlineStr">
         <is>
           <t>images/track_04/a1_s04_seg26_boy.jpg</t>
+        </is>
+      </c>
+      <c r="L28" s="29" t="inlineStr">
+        <is>
+          <t>videos/T4/t4_seg_26.mp4</t>
         </is>
       </c>
     </row>

--- a/web_app/Album1_Dance_Production_Spec.xlsx
+++ b/web_app/Album1_Dance_Production_Spec.xlsx
@@ -25026,7 +25026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -25040,6 +25040,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -25105,6 +25106,11 @@
           <t>首張圖片路徑 (9:16 720p)</t>
         </is>
       </c>
+      <c r="L2" s="28" t="inlineStr">
+        <is>
+          <t>AI 影片動畫路徑 (T5 目錄)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -25158,6 +25164,11 @@
           <t>images/track_05/a1_s05_seg01_girl.jpg</t>
         </is>
       </c>
+      <c r="L3" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_01.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -25211,6 +25222,11 @@
           <t>images/track_05/a1_s05_seg02_girl.jpg</t>
         </is>
       </c>
+      <c r="L4" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_02.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
@@ -25264,6 +25280,11 @@
           <t>images/track_05/a1_s05_seg03_girl.jpg</t>
         </is>
       </c>
+      <c r="L5" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_03.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -25317,6 +25338,11 @@
           <t>images/track_05/a1_s05_seg04_girl.jpg</t>
         </is>
       </c>
+      <c r="L6" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_04.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -25370,6 +25396,11 @@
           <t>images/track_05/a1_s05_seg05_girl.jpg</t>
         </is>
       </c>
+      <c r="L7" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_05.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -25423,6 +25454,11 @@
           <t>images/track_05/a1_s05_seg06_girl.jpg</t>
         </is>
       </c>
+      <c r="L8" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_06.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -25476,6 +25512,11 @@
           <t>images/track_05/a1_s05_seg07_girl.jpg</t>
         </is>
       </c>
+      <c r="L9" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_07.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -25529,6 +25570,11 @@
           <t>images/track_05/a1_s05_seg08_girl.jpg</t>
         </is>
       </c>
+      <c r="L10" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_08.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -25582,6 +25628,11 @@
           <t>images/track_05/a1_s05_seg09_girl.jpg</t>
         </is>
       </c>
+      <c r="L11" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_09.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -25635,6 +25686,11 @@
           <t>images/track_05/a1_s05_seg10_girl.jpg</t>
         </is>
       </c>
+      <c r="L12" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_10.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -25688,6 +25744,11 @@
           <t>images/track_05/a1_s05_seg11_girl.jpg</t>
         </is>
       </c>
+      <c r="L13" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_11.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -25741,6 +25802,11 @@
           <t>images/track_05/a1_s05_seg12_girl.jpg</t>
         </is>
       </c>
+      <c r="L14" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_12.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
@@ -25794,6 +25860,11 @@
           <t>images/track_05/a1_s05_seg13_girl.jpg</t>
         </is>
       </c>
+      <c r="L15" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_13.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -25847,6 +25918,11 @@
           <t>images/track_05/a1_s05_seg14_girl.jpg</t>
         </is>
       </c>
+      <c r="L16" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_14.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -25900,6 +25976,11 @@
           <t>images/track_05/a1_s05_seg15_girl.jpg</t>
         </is>
       </c>
+      <c r="L17" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_15.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -25953,6 +26034,11 @@
           <t>images/track_05/a1_s05_seg16_girl.jpg</t>
         </is>
       </c>
+      <c r="L18" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_16.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -26006,6 +26092,11 @@
           <t>images/track_05/a1_s05_seg17_girl.jpg</t>
         </is>
       </c>
+      <c r="L19" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_17.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -26059,6 +26150,11 @@
           <t>images/track_05/a1_s05_seg18_girl.jpg</t>
         </is>
       </c>
+      <c r="L20" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_18.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -26112,6 +26208,11 @@
           <t>images/track_05/a1_s05_seg19_girl.jpg</t>
         </is>
       </c>
+      <c r="L21" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_19.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -26165,6 +26266,11 @@
           <t>images/track_05/a1_s05_seg20_girl.jpg</t>
         </is>
       </c>
+      <c r="L22" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_20.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -26218,6 +26324,11 @@
           <t>images/track_05/a1_s05_seg21_girl.jpg</t>
         </is>
       </c>
+      <c r="L23" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_21.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -26271,6 +26382,11 @@
           <t>images/track_05/a1_s05_seg22_girl.jpg</t>
         </is>
       </c>
+      <c r="L24" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_22.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -26324,6 +26440,11 @@
           <t>images/track_05/a1_s05_seg23_girl.jpg</t>
         </is>
       </c>
+      <c r="L25" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_23.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
@@ -26377,6 +26498,11 @@
           <t>images/track_05/a1_s05_seg24_girl.jpg</t>
         </is>
       </c>
+      <c r="L26" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_24.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -26430,6 +26556,11 @@
           <t>images/track_05/a1_s05_seg25_girl.jpg</t>
         </is>
       </c>
+      <c r="L27" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_25.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -26481,6 +26612,11 @@
       <c r="K28" s="20" t="inlineStr">
         <is>
           <t>images/track_05/a1_s05_seg26_girl.jpg</t>
+        </is>
+      </c>
+      <c r="L28" s="29" t="inlineStr">
+        <is>
+          <t>videos/T5/t5_seg_26.mp4</t>
         </is>
       </c>
     </row>
